--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484108_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484108_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2498</v>
+        <v>7.8503</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4423</v>
+        <v>4.0147</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8075</v>
+        <v>3.8356</v>
       </c>
       <c r="G2" t="n">
         <v>4.6772</v>
@@ -610,13 +610,13 @@
         <v>1.1903</v>
       </c>
       <c r="S2" t="n">
-        <v>1.311</v>
+        <v>1.9115</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3173</v>
+        <v>0.2552</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6283</v>
+        <v>1.6564</v>
       </c>
       <c r="V2" t="n">
         <v>0.0713</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9836</v>
+        <v>5.2029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1323</v>
+        <v>3.2266</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8513</v>
+        <v>1.9762</v>
       </c>
       <c r="G3" t="n">
-        <v>6.0102</v>
+        <v>1.9284</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3918</v>
+        <v>2.0658</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6184</v>
+        <v>-0.1374</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7371</v>
+        <v>1.1452</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8937</v>
+        <v>1.9758</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8434</v>
+        <v>-0.8306</v>
       </c>
       <c r="M3" t="n">
-        <v>2.2731</v>
+        <v>0.7832</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4981</v>
+        <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.775</v>
+        <v>0.6932</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.9758</v>
+        <v>0.9919</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.9677</v>
+        <v>-0.1984</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9492</v>
+        <v>0.2069</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3629</v>
+        <v>0.2041</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5863</v>
+        <v>0.0027</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.86</v>
+        <v>4.3026</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1643</v>
+        <v>-0.0718</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6957</v>
+        <v>4.3744</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9284</v>
+        <v>6.0102</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0658</v>
+        <v>3.3918</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1374</v>
+        <v>2.6184</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1452</v>
+        <v>3.7371</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9758</v>
+        <v>2.8937</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8306</v>
+        <v>0.8434</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7832</v>
+        <v>2.2731</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09</v>
+        <v>0.4981</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6932</v>
+        <v>1.775</v>
       </c>
       <c r="P4" t="n">
+        <v>-2.9758</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-3.9677</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.9919</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.1984</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.1903</v>
-      </c>
       <c r="S4" t="n">
-        <v>-0.136</v>
+        <v>1.2682</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1418</v>
+        <v>0.1588</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2778</v>
+        <v>1.1094</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. DE LEON</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8432</v>
+        <v>2.8731</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2587</v>
+        <v>1.3671</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5846</v>
+        <v>1.506</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1102</v>
+        <v>2.3243</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2975</v>
+        <v>0.9472</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8127</v>
+        <v>1.3771</v>
       </c>
       <c r="J5" t="n">
-        <v>2.127</v>
+        <v>1.4804</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6812</v>
+        <v>0.3884</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4458</v>
+        <v>1.092</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9832</v>
+        <v>0.8439</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3837</v>
+        <v>0.5588</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3669</v>
+        <v>0.2851</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.1741</v>
+        <v>0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9677</v>
+        <v>-0.1984</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9667</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2301</v>
+        <v>0.0851</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7366</v>
+        <v>0.5313</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9405</v>
+        <v>-0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0713</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>R. DE LEON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2787</v>
+        <v>2.7924</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8569</v>
+        <v>-0.4555</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4218</v>
+        <v>3.2479</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3243</v>
+        <v>3.1102</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9472</v>
+        <v>0.2975</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3771</v>
+        <v>2.8127</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4804</v>
+        <v>2.127</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3884</v>
+        <v>0.6812</v>
       </c>
       <c r="L6" t="n">
-        <v>1.092</v>
+        <v>1.4458</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8439</v>
+        <v>0.9832</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5588</v>
+        <v>-0.3837</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2851</v>
+        <v>1.3669</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>-3.1741</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>-3.9677</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0221</v>
+        <v>1.9158</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4251</v>
+        <v>0.5159</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4471</v>
+        <v>1.3999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.266</v>
+        <v>0.9405</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.266</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0978</v>
+        <v>2.1806</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5904</v>
+        <v>-0.7321</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6883</v>
+        <v>2.9127</v>
       </c>
       <c r="G7" t="n">
         <v>4.8782</v>
@@ -1000,13 +1000,13 @@
         <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8185</v>
+        <v>0.9012</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4989</v>
+        <v>0.3572</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3196</v>
+        <v>0.544</v>
       </c>
       <c r="V7" t="n">
         <v>-1.615</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.763</v>
+        <v>1.6584</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3632</v>
+        <v>-0.1592</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1262</v>
+        <v>1.8176</v>
       </c>
       <c r="G8" t="n">
         <v>1.7081</v>
@@ -1078,13 +1078,13 @@
         <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5311</v>
+        <v>0.4265</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3741</v>
+        <v>-0.17</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9051</v>
+        <v>0.5965</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6745</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>A. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3242</v>
+        <v>1.2849</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2506</v>
+        <v>0.3192</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0737</v>
+        <v>0.9657</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0575</v>
+        <v>1.9719</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6027</v>
+        <v>2.8931</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4548</v>
+        <v>-0.9212</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9003</v>
+        <v>0.9936</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8602</v>
+        <v>2.8735</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0402</v>
+        <v>-1.8799</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1572</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2574</v>
+        <v>0.0195</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4146</v>
+        <v>0.9588</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.1822</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1741</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1829</v>
+        <v>1.2498</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2584</v>
+        <v>0.3175</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.9323</v>
       </c>
       <c r="V9" t="n">
-        <v>0.266</v>
+        <v>-1.7384</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. POU BLINNIKOV</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5248</v>
+        <v>0.6443</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4971</v>
+        <v>-0.4013</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0218</v>
+        <v>1.0456</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9719</v>
+        <v>2.0575</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8931</v>
+        <v>1.6027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9212</v>
+        <v>0.4548</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9936</v>
+        <v>1.9003</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8735</v>
+        <v>1.8602</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8799</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.1572</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0195</v>
+        <v>-0.2574</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9588</v>
+        <v>0.4146</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1984</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4897</v>
+        <v>0.503</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4988</v>
+        <v>0.6065</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9883999999999999</v>
+        <v>-0.1035</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7384</v>
+        <v>0.266</v>
       </c>
       <c r="W10" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.7384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. MARTINEZ JANER</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7876</v>
+        <v>-0.8885</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4114</v>
+        <v>-2.8323</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6238</v>
+        <v>1.9438</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8858</v>
+        <v>0.2868</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3808</v>
+        <v>0.4786</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4949</v>
+        <v>-0.1918</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9119</v>
+        <v>-1.557</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9922</v>
+        <v>-0.277</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0803</v>
+        <v>-1.2801</v>
       </c>
       <c r="M11" t="n">
-        <v>0.026</v>
+        <v>1.8439</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3886</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4146</v>
+        <v>1.0883</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1741</v>
+        <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4788</v>
+        <v>-0.445</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0714</v>
+        <v>-0.2834</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4075</v>
+        <v>-0.1616</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6032</v>
+        <v>-0.532</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BRADLEY MAYOL</t>
+          <t>B. MARTINEZ JANER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4491</v>
+        <v>-1.1512</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5293</v>
+        <v>-2.8592</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0801</v>
+        <v>1.708</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8078</v>
+        <v>-0.8858</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.222</v>
+        <v>-1.3808</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5858</v>
+        <v>0.4949</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2799</v>
+        <v>-0.9119</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0403</v>
+        <v>-0.9922</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3202</v>
+        <v>0.0803</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5279</v>
+        <v>0.026</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2623</v>
+        <v>-0.3886</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2656</v>
+        <v>0.4146</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1984</v>
+        <v>-3.1741</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2483</v>
+        <v>1.1152</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.051</v>
+        <v>0.6236</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1973</v>
+        <v>0.4916</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4085</v>
+        <v>0.6032</v>
       </c>
       <c r="W12" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="X12" t="n">
         <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.4085</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>J. BRADLEY MAYOL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4853</v>
+        <v>-1.2349</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0364</v>
+        <v>-1.4273</v>
       </c>
       <c r="F13" t="n">
-        <v>1.551</v>
+        <v>0.1924</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2868</v>
+        <v>-1.8078</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4786</v>
+        <v>-0.222</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1918</v>
+        <v>-1.5858</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.557</v>
+        <v>-1.2799</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.277</v>
+        <v>0.0403</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2801</v>
+        <v>-1.3202</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8439</v>
+        <v>-0.5279</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7554999999999999</v>
+        <v>-0.2623</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0883</v>
+        <v>-0.2656</v>
       </c>
       <c r="P13" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-0.1984</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-0.9919</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0418</v>
+        <v>-0.034</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4874</v>
+        <v>0.051</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5544</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.532</v>
+        <v>0.4085</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.532</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.2031</v>
+        <v>25.5149</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3226999999999998</v>
+        <v>-0.01109999999999967</v>
       </c>
       <c r="F14" t="n">
-        <v>25.5258</v>
+        <v>25.5259</v>
       </c>
       <c r="G14" t="n">
         <v>26.2592</v>
@@ -1525,13 +1525,13 @@
         <v>11.6224</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1411</v>
+        <v>3.141100000000001</v>
       </c>
       <c r="M14" t="n">
         <v>11.4958</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5476000000000001</v>
+        <v>0.5475999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>10.948</v>
@@ -1546,16 +1546,16 @@
         <v>10.911</v>
       </c>
       <c r="S14" t="n">
-        <v>9.323899999999997</v>
+        <v>9.635499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4098</v>
+        <v>2.721500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>6.914</v>
+        <v>6.913999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4607</v>
+        <v>-0.4607000000000004</v>
       </c>
       <c r="W14" t="n">
         <v>3.3343</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3455</v>
+        <v>2.2876</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6932</v>
+        <v>1.3871</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6523</v>
+        <v>0.9005</v>
       </c>
       <c r="G15" t="n">
         <v>0.5475</v>
@@ -1624,13 +1624,13 @@
         <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2652</v>
+        <v>-0.323</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1076</v>
+        <v>-0.4137</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1576</v>
+        <v>0.0906</v>
       </c>
       <c r="V15" t="n">
         <v>0.6745</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0717</v>
+        <v>1.382</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4412</v>
+        <v>1.3391</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3695</v>
+        <v>0.0429</v>
       </c>
       <c r="G16" t="n">
         <v>-1.9393</v>
@@ -1702,13 +1702,13 @@
         <v>2.7774</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4335</v>
+        <v>-0.1232</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1982</v>
+        <v>-0.3003</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2353</v>
+        <v>0.1771</v>
       </c>
       <c r="V16" t="n">
         <v>1.0639</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.766</v>
+        <v>-0.4259</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5336</v>
+        <v>-0.3296</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2323</v>
+        <v>-0.0963</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4462</v>
@@ -1780,13 +1780,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7085</v>
+        <v>-0.3684</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4761</v>
+        <v>-0.272</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2324</v>
+        <v>-0.0964</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6032</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1879</v>
+        <v>-1.272</v>
       </c>
       <c r="E18" t="n">
         <v>-1.5549</v>
       </c>
       <c r="F18" t="n">
-        <v>0.367</v>
+        <v>0.2828</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2593</v>
@@ -1858,13 +1858,13 @@
         <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2658</v>
+        <v>-0.35</v>
       </c>
       <c r="T18" t="n">
         <v>-0.6235000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3576</v>
+        <v>0.2734</v>
       </c>
       <c r="V18" t="n">
         <v>-0.266</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8805</v>
+        <v>-2.3296</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1686</v>
+        <v>-2.0665</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7119</v>
+        <v>-0.263</v>
       </c>
       <c r="G19" t="n">
         <v>-2.9919</v>
@@ -1936,13 +1936,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.4837</v>
+        <v>-1.9328</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.621</v>
+        <v>-1.5189</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8627</v>
+        <v>-0.4139</v>
       </c>
       <c r="V19" t="n">
         <v>1.2065</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2948</v>
+        <v>-2.7864</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3672</v>
+        <v>-4.1631</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0723</v>
+        <v>1.3767</v>
       </c>
       <c r="G20" t="n">
         <v>-1.648</v>
@@ -2014,13 +2014,13 @@
         <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2538</v>
+        <v>-0.7453</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9635</v>
+        <v>-0.7594</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2903</v>
+        <v>0.0141</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1947</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0601</v>
+        <v>-3.6145</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.2018</v>
+        <v>-4.6917</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1417</v>
+        <v>1.0772</v>
       </c>
       <c r="G21" t="n">
         <v>-5.7521</v>
@@ -2092,13 +2092,13 @@
         <v>4.1661</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7605</v>
+        <v>-1.315</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5642</v>
+        <v>-1.0541</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1963</v>
+        <v>-0.2609</v>
       </c>
       <c r="V21" t="n">
         <v>1.6671</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0786</v>
+        <v>-5.3149</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7381</v>
+        <v>-4.9422</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3404</v>
+        <v>-0.3727</v>
       </c>
       <c r="G22" t="n">
         <v>-6.5138</v>
@@ -2170,13 +2170,13 @@
         <v>2.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.747</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4817</v>
+        <v>-0.6857</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2654</v>
+        <v>-0.2976</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>H. OLAGUIBE GONZALEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2868</v>
+        <v>-5.8582</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2596</v>
+        <v>-4.4284</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0272</v>
+        <v>-1.4298</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.3105</v>
+        <v>-2.9457</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.0514</v>
+        <v>-1.6178</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2591</v>
+        <v>-1.3279</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.6726</v>
+        <v>-0.7046</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.9924</v>
+        <v>-0.0244</v>
       </c>
       <c r="L23" t="n">
         <v>-0.6802</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6379</v>
+        <v>-2.2411</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.059</v>
+        <v>-1.5934</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4211</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P23" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0318</v>
+        <v>-1.23</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3969</v>
+        <v>-0.8671</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3651</v>
+        <v>-0.3629</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2065</v>
+        <v>-1.881</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X23" t="n">
         <v>-1.2065</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. OLAGUIBE GONZALEZ</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0657</v>
+        <v>-5.9109</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8366</v>
+        <v>-6.0758</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2292</v>
+        <v>0.1649</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9457</v>
+        <v>-4.3105</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6178</v>
+        <v>-4.0514</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3279</v>
+        <v>-0.2591</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7046</v>
+        <v>-3.6726</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0244</v>
+        <v>-2.9924</v>
       </c>
       <c r="L24" t="n">
         <v>-0.6802</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2411</v>
+        <v>-0.6379</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5934</v>
+        <v>-1.059</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.4211</v>
       </c>
       <c r="P24" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3806</v>
+        <v>2.1822</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4374</v>
+        <v>-0.5923</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2752</v>
+        <v>-0.4193</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1622</v>
+        <v>-0.173</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.881</v>
+        <v>-1.2065</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>-1.2065</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-25.2032</v>
+        <v>-23.8428</v>
       </c>
       <c r="E25" t="n">
         <v>-25.526</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3228</v>
+        <v>1.6832</v>
       </c>
       <c r="G25" t="n">
         <v>-26.2593</v>
@@ -2404,16 +2404,16 @@
         <v>20.8305</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.323599999999999</v>
+        <v>-7.9634</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.9141</v>
+        <v>-6.913999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.4097</v>
+        <v>-1.0495</v>
       </c>
       <c r="V25" t="n">
-        <v>0.4605999999999997</v>
+        <v>0.4605999999999999</v>
       </c>
       <c r="W25" t="n">
         <v>3.795</v>
